--- a/TestData/TMTI0055011_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFVALOBOpportunityEngagement.xlsx
+++ b/TestData/TMTI0055011_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFVALOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8CCB78-CDEE-4E85-AF5F-488A17920D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812F5EB7-E21B-4C64-8022-0EE4EC519F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" firstSheet="1" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14640" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -289,9 +289,6 @@
     <t>Preston Wolf</t>
   </si>
   <si>
-    <t>Rich Bowman</t>
-  </si>
-  <si>
     <t>Rittik Chakrabarti</t>
   </si>
   <si>
@@ -338,6 +335,9 @@
   </si>
   <si>
     <t>Mark Schade</t>
+  </si>
+  <si>
+    <t>Kyle Zhao</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1008,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1043,7 +1043,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -1098,56 +1098,57 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1161,12 +1162,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1185,18 +1186,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTI0055011_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFVALOBOpportunityEngagement.xlsx
+++ b/TestData/TMTI0055011_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFVALOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812F5EB7-E21B-4C64-8022-0EE4EC519F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F12FEC-8F32-41F6-BE9B-AA88C33F7D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14640" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>

--- a/TestData/TMTI0055011_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFVALOBOpportunityEngagement.xlsx
+++ b/TestData/TMTI0055011_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFVALOBOpportunityEngagement.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F12FEC-8F32-41F6-BE9B-AA88C33F7D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801F9B47-6AA4-4AA9-AF75-F86F6BF9E099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AddContact" sheetId="3" r:id="rId3"/>
-    <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId4"/>
-    <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId5"/>
-    <sheet name="OverlimitMessage" sheetId="6" r:id="rId6"/>
+    <sheet name="AppName" sheetId="7" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="8" r:id="rId3"/>
+    <sheet name="Users" sheetId="2" r:id="rId4"/>
+    <sheet name="AddContact" sheetId="3" r:id="rId5"/>
+    <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId6"/>
+    <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId7"/>
+    <sheet name="OverlimitMessage" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="106">
   <si>
     <t>Client</t>
   </si>
@@ -199,9 +201,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Danielle Morello</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -338,6 +337,30 @@
   </si>
   <si>
     <t>Kyle Zhao</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Opportunities</t>
+  </si>
+  <si>
+    <t>William Peluchiwski</t>
+  </si>
+  <si>
+    <t>Liz Hedgcock</t>
+  </si>
+  <si>
+    <t>Indrajeet Singh</t>
+  </si>
+  <si>
+    <t>Admin</t>
   </si>
 </sst>
 </file>
@@ -911,24 +934,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC86E6DB-62E2-4C2E-810E-7BAC0D41D896}">
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -937,34 +954,94 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F754C49E-B17C-430C-9259-61A8E9074D7F}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -972,25 +1049,25 @@
         <v>44</v>
       </c>
       <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +1075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1008,142 +1085,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1162,12 +1239,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1175,7 +1252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1186,18 +1263,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTI0055011_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFVALOBOpportunityEngagement.xlsx
+++ b/TestData/TMTI0055011_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFVALOBOpportunityEngagement.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8CCB78-CDEE-4E85-AF5F-488A17920D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801F9B47-6AA4-4AA9-AF75-F86F6BF9E099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" firstSheet="1" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4F41EB50-8C78-4F9F-A1D4-8B783E020697}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
-    <sheet name="Users" sheetId="2" r:id="rId2"/>
-    <sheet name="AddContact" sheetId="3" r:id="rId3"/>
-    <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId4"/>
-    <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId5"/>
-    <sheet name="OverlimitMessage" sheetId="6" r:id="rId6"/>
+    <sheet name="AppName" sheetId="7" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="8" r:id="rId3"/>
+    <sheet name="Users" sheetId="2" r:id="rId4"/>
+    <sheet name="AddContact" sheetId="3" r:id="rId5"/>
+    <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId6"/>
+    <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId7"/>
+    <sheet name="OverlimitMessage" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="106">
   <si>
     <t>Client</t>
   </si>
@@ -199,9 +201,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Danielle Morello</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -289,9 +288,6 @@
     <t>Preston Wolf</t>
   </si>
   <si>
-    <t>Rich Bowman</t>
-  </si>
-  <si>
     <t>Rittik Chakrabarti</t>
   </si>
   <si>
@@ -338,6 +334,33 @@
   </si>
   <si>
     <t>Mark Schade</t>
+  </si>
+  <si>
+    <t>Kyle Zhao</t>
+  </si>
+  <si>
+    <t>App Name</t>
+  </si>
+  <si>
+    <t>HL Banker</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Opportunities</t>
+  </si>
+  <si>
+    <t>William Peluchiwski</t>
+  </si>
+  <si>
+    <t>Liz Hedgcock</t>
+  </si>
+  <si>
+    <t>Indrajeet Singh</t>
+  </si>
+  <si>
+    <t>Admin</t>
   </si>
 </sst>
 </file>
@@ -911,24 +934,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC86E6DB-62E2-4C2E-810E-7BAC0D41D896}">
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -937,34 +954,94 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F754C49E-B17C-430C-9259-61A8E9074D7F}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398AFF69-DCD2-4291-899D-46D247625F33}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157DEAB0-0FBE-44C7-9D14-EA88B9DE7C90}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -972,25 +1049,25 @@
         <v>44</v>
       </c>
       <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
         <v>61</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +1075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E8CB76-FB8A-4028-8972-B88CE86EF1D8}">
   <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1008,150 +1085,151 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6F88B60-A419-401F-AD7F-AECB9C160562}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1161,12 +1239,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1174,7 +1252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41831907-90E4-4F72-A4FC-60E82CC27F92}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1185,18 +1263,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
